--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486985_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486985_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7682</v>
+        <v>3.3863</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2535</v>
+        <v>0.8278</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5146</v>
+        <v>2.5585</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5605</v>
+        <v>0.3515</v>
       </c>
       <c r="H2" t="n">
-        <v>1.732</v>
+        <v>-0.1328</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8285</v>
+        <v>0.4843</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6334</v>
+        <v>0.2689</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1996</v>
+        <v>0.8083</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4338</v>
+        <v>-0.5395</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9271</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4676</v>
+        <v>-0.9412</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3947</v>
+        <v>1.0238</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.616</v>
+        <v>0.616</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R2" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1728</v>
+        <v>0.6509</v>
       </c>
       <c r="T2" t="n">
-        <v>0.612</v>
+        <v>0.0231</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5608</v>
+        <v>0.6278</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3491</v>
+        <v>1.7679</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2402</v>
+        <v>1.7679</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8881</v>
+        <v>3.3267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4482</v>
+        <v>1.901</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4399</v>
+        <v>1.4257</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3515</v>
+        <v>3.5605</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1328</v>
+        <v>1.732</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4843</v>
+        <v>1.8285</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2689</v>
+        <v>2.6334</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8083</v>
+        <v>2.1996</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5395</v>
+        <v>0.4338</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.9271</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9412</v>
+        <v>-0.4676</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0238</v>
+        <v>1.3947</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1526</v>
+        <v>0.7313</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3566</v>
+        <v>0.2594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5092</v>
+        <v>0.4719</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7679</v>
+        <v>-0.3491</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7679</v>
+        <v>0.2402</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.018</v>
+        <v>1.3445</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5649</v>
+        <v>1.84</v>
       </c>
       <c r="F4" t="n">
-        <v>0.453</v>
+        <v>-0.4955</v>
       </c>
       <c r="G4" t="n">
         <v>4.229</v>
@@ -766,13 +766,13 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3782</v>
+        <v>1.7047</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4144</v>
+        <v>0.6894</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9639</v>
+        <v>1.0153</v>
       </c>
       <c r="V4" t="n">
         <v>-2.9466</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1797</v>
+        <v>0.991</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0606</v>
+        <v>1.8126</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8809</v>
+        <v>-0.8216</v>
       </c>
       <c r="G5" t="n">
         <v>1.1147</v>
@@ -844,13 +844,13 @@
         <v>1.0267</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1553</v>
+        <v>0.9666</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4066</v>
+        <v>0.1587</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7487</v>
+        <v>0.8079</v>
       </c>
       <c r="V5" t="n">
         <v>-2.117</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1567</v>
+        <v>0.8031</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6516</v>
+        <v>-0.2719</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8083</v>
+        <v>1.0751</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5368000000000001</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1361</v>
+        <v>0.5104</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2249</v>
+        <v>0.1548</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0888</v>
+        <v>0.3556</v>
       </c>
       <c r="V6" t="n">
         <v>0.8295</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5833</v>
+        <v>-0.2176</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8149</v>
+        <v>-0.3306</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2316</v>
+        <v>0.113</v>
       </c>
       <c r="G7" t="n">
         <v>1.1289</v>
@@ -1000,13 +1000,13 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8586</v>
+        <v>1.2243</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2907</v>
+        <v>0.1936</v>
       </c>
       <c r="U7" t="n">
-        <v>1.1493</v>
+        <v>1.0308</v>
       </c>
       <c r="V7" t="n">
         <v>-3.1868</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4978</v>
+        <v>-1.418</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5704</v>
+        <v>-2.6091</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0726</v>
+        <v>1.1911</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0035</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2921</v>
+        <v>0.372</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3021</v>
+        <v>0.2634</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.01</v>
+        <v>0.1086</v>
       </c>
       <c r="V8" t="n">
         <v>0.2402</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7024</v>
+        <v>-1.49</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5829</v>
+        <v>-2.7263</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.2362</v>
       </c>
       <c r="G9" t="n">
         <v>0.2616</v>
@@ -1156,13 +1156,13 @@
         <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.348</v>
+        <v>-0.1356</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1122</v>
+        <v>-0.0311</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4602</v>
+        <v>-0.1045</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8212</v>
+        <v>-3.0831</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1054</v>
+        <v>-4.2488</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2842</v>
+        <v>1.1656</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7499</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>0.75</v>
+        <v>0.4881</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6778</v>
+        <v>0.5345</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0722</v>
+        <v>-0.0464</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5521</v>
+        <v>-3.1305</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5039</v>
+        <v>-2.4381</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0481</v>
+        <v>-0.6924</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6737</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4061</v>
+        <v>0.0155</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4147</v>
+        <v>-0.3489</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0086</v>
+        <v>0.3643</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1461000000000001</v>
+        <v>0.5124000000000009</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.9019</v>
+        <v>-6.243399999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.755700000000001</v>
+        <v>6.7557</v>
       </c>
       <c r="G12" t="n">
         <v>4.6823</v>
@@ -1390,10 +1390,10 @@
         <v>13.3472</v>
       </c>
       <c r="S12" t="n">
-        <v>5.8694</v>
+        <v>6.5282</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2382</v>
+        <v>1.8969</v>
       </c>
       <c r="U12" t="n">
         <v>4.6313</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.343</v>
+        <v>2.1154</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.2563</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5773</v>
+        <v>0.8591</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2701</v>
+        <v>-1.8486</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2645</v>
+        <v>-1.2356</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9943</v>
+        <v>-0.6131</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3424</v>
+        <v>-0.4429</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9213</v>
+        <v>-0.2452</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.579</v>
+        <v>-0.1977</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0722</v>
+        <v>-1.4057</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3431</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-0.4154</v>
       </c>
       <c r="P13" t="n">
-        <v>0.616</v>
+        <v>1.6427</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R13" t="n">
         <v>2.6694</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4568</v>
+        <v>-1.2146</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2981</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1587</v>
+        <v>-0.4046</v>
       </c>
       <c r="V13" t="n">
+        <v>3.5359</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.5359</v>
+      </c>
+      <c r="X13" t="n">
         <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1786</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-1.1786</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1361</v>
+        <v>1.868</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4694</v>
+        <v>-1.1556</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6054</v>
+        <v>3.0236</v>
       </c>
       <c r="G14" t="n">
         <v>-2.0943</v>
@@ -1546,13 +1546,13 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4356</v>
+        <v>0.1676</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9649</v>
+        <v>-0.6511</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4005</v>
+        <v>0.8187</v>
       </c>
       <c r="V14" t="n">
         <v>2.3573</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4983</v>
+        <v>1.8252</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8379</v>
+        <v>0.138</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6604</v>
+        <v>1.6872</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8486</v>
+        <v>1.2701</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2356</v>
+        <v>2.2645</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6131</v>
+        <v>-0.9943</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4429</v>
+        <v>1.3424</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2452</v>
+        <v>1.9213</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1977</v>
+        <v>-0.579</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4057</v>
+        <v>-0.0722</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9903999999999999</v>
+        <v>0.3431</v>
       </c>
       <c r="O15" t="n">
         <v>-0.4154</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R15" t="n">
         <v>2.6694</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8317</v>
+        <v>-0.061</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2284</v>
+        <v>-0.3296</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6032999999999999</v>
+        <v>0.2686</v>
       </c>
       <c r="V15" t="n">
-        <v>3.5359</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.5359</v>
+        <v>1.1786</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2773</v>
+        <v>0.619</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6446</v>
+        <v>-1.54</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9219</v>
+        <v>2.1591</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3805</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5742</v>
+        <v>-0.2325</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6587</v>
+        <v>-0.5541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.3216</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5398</v>
+        <v>0.4293</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6181</v>
+        <v>-0.3303</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3165</v>
+        <v>0.1094</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0809</v>
+        <v>0.1358</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3973</v>
+        <v>-0.0264</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8034</v>
+        <v>1.1449</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8298</v>
+        <v>0.6847</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0264</v>
+        <v>0.4602</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1198</v>
+        <v>-1.0355</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7489</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3709</v>
+        <v>-0.4866</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2033</v>
+        <v>-1.3677</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5229</v>
+        <v>-0.9106</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3196</v>
+        <v>-0.457</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2402</v>
+        <v>1.7679</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2402</v>
+        <v>2.2484</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4659</v>
+        <v>-0.2439</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2201</v>
+        <v>1.226</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-1.4698</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1094</v>
+        <v>-0.3165</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1358</v>
+        <v>0.0809</v>
       </c>
       <c r="I18" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.8034</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.8298</v>
+      </c>
+      <c r="L18" t="n">
         <v>-0.0264</v>
       </c>
-      <c r="J18" t="n">
-        <v>1.1449</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.6847</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4602</v>
-      </c>
       <c r="M18" t="n">
-        <v>-1.0355</v>
+        <v>-2.1198</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-1.7489</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4866</v>
+        <v>-0.3709</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4107</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9326</v>
+        <v>0.0377</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1198</v>
+        <v>0.2091</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8128</v>
+        <v>-0.1714</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7679</v>
+        <v>0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2484</v>
+        <v>0.2402</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1233</v>
+        <v>-0.8182</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4853</v>
+        <v>-3.1715</v>
       </c>
       <c r="F19" t="n">
-        <v>2.362</v>
+        <v>2.3533</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0951</v>
@@ -1936,13 +1936,13 @@
         <v>2.4641</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7879</v>
+        <v>-1.4828</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.5151</v>
+        <v>-1.2012</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2729</v>
+        <v>-0.2816</v>
       </c>
       <c r="V19" t="n">
         <v>0.3491</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8295</v>
+        <v>-2.1241</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9501</v>
+        <v>-2.4731</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1206</v>
+        <v>0.349</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1405</v>
@@ -2014,13 +2014,13 @@
         <v>2.6694</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1406</v>
+        <v>-0.154</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5615</v>
+        <v>0.0385</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4209</v>
+        <v>-0.1925</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4189</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6114</v>
+        <v>-2.4475</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5697</v>
+        <v>-1.4651</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0416</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1863</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9795</v>
+        <v>-0.8156</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.527</v>
+        <v>-0.4224</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4525</v>
+        <v>-0.3932</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2402</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1462999999999997</v>
+        <v>0.8929000000000005</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.7557</v>
+        <v>-6.755700000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>6.9019</v>
+        <v>7.6488</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6823</v>
@@ -2143,7 +2143,7 @@
         <v>-8.5905</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8330999999999997</v>
+        <v>0.8331</v>
       </c>
       <c r="K22" t="n">
         <v>7.465300000000001</v>
@@ -2170,13 +2170,13 @@
         <v>17.454</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.8696</v>
+        <v>-5.1229</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.631399999999999</v>
+        <v>-4.6314</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.2383</v>
+        <v>-0.4914000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>6.5913</v>
